--- a/output_data/charts/crashSeverityByType-Region10.xlsx
+++ b/output_data/charts/crashSeverityByType-Region10.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>Share of fatal crashes</t>
   </si>
@@ -52,40 +52,37 @@
     <t>Overturning</t>
   </si>
   <si>
+    <t>Parked Vehicle</t>
+  </si>
+  <si>
     <t>Pedalcycles</t>
   </si>
   <si>
-    <t>Parked Vehicle</t>
+    <t>Animal</t>
   </si>
   <si>
     <t>Other Non-Collision</t>
   </si>
   <si>
-    <t>Animal</t>
-  </si>
-  <si>
     <t>Right Turn</t>
   </si>
   <si>
+    <t>Unknown</t>
+  </si>
+  <si>
+    <t>Other Object</t>
+  </si>
+  <si>
     <t>Sideswipe - Meeting</t>
   </si>
   <si>
-    <t>Unknown</t>
-  </si>
-  <si>
     <t>Backing</t>
   </si>
   <si>
+    <t>Other Non-Vehicle</t>
+  </si>
+  <si>
     <t>Train</t>
-  </si>
-  <si>
-    <t>Other Object</t>
-  </si>
-  <si>
-    <t>Falling From Or In Vehicle</t>
-  </si>
-  <si>
-    <t>Other Non-Vehicle</t>
   </si>
 </sst>
 </file>
@@ -218,9 +215,9 @@
           </c:spPr>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$A$2:$A$21</c:f>
+              <c:f>Sheet1!$A$2:$A$20</c:f>
               <c:strCache>
-                <c:ptCount val="20"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>Fixed Object</c:v>
                 </c:pt>
@@ -246,108 +243,102 @@
                   <c:v>Overturning</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>Parked Vehicle</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>Pedalcycles</c:v>
                 </c:pt>
-                <c:pt idx="9">
-                  <c:v>Parked Vehicle</c:v>
-                </c:pt>
                 <c:pt idx="10">
+                  <c:v>Animal</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>Other Non-Collision</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>Animal</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>Right Turn</c:v>
                 </c:pt>
                 <c:pt idx="13">
+                  <c:v>Unknown</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Other Object</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>Sideswipe - Meeting</c:v>
                 </c:pt>
-                <c:pt idx="14">
-                  <c:v>Unknown</c:v>
-                </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>Backing</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
+                  <c:v>Other Non-Vehicle</c:v>
+                </c:pt>
+                <c:pt idx="18">
                   <c:v>Train</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>Other Object</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>Falling From Or In Vehicle</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>Other Non-Vehicle</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$21</c:f>
+              <c:f>Sheet1!$B$2:$B$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>30.02915451895043</c:v>
+                  <c:v>28.55740922473013</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>17.58989310009718</c:v>
+                  <c:v>17.46810598626104</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>12.53644314868805</c:v>
+                  <c:v>14.22963689892051</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>11.07871720116618</c:v>
+                  <c:v>11.48184494602552</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6.997084548104956</c:v>
+                  <c:v>7.065750736015702</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6.608357628765791</c:v>
+                  <c:v>6.182531894013739</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.859086491739554</c:v>
+                  <c:v>5.397448478900883</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.109815354713314</c:v>
+                  <c:v>3.042198233562316</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.84645286686103</c:v>
+                  <c:v>1.962708537782139</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.652089407191448</c:v>
+                  <c:v>1.275760549558391</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.068999028182702</c:v>
+                  <c:v>1.079489695780177</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.9718172983479106</c:v>
+                  <c:v>0.8832188420019628</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.9718172983479106</c:v>
+                  <c:v>0.7850834151128557</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.1943634596695821</c:v>
+                  <c:v>0.2944062806673209</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.1943634596695821</c:v>
+                  <c:v>0.09813542688910697</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.09718172983479105</c:v>
+                  <c:v>0.09813542688910697</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.09718172983479105</c:v>
+                  <c:v>0.09813542688910697</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.09718172983479105</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="19">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -378,9 +369,9 @@
           </c:spPr>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$A$2:$A$21</c:f>
+              <c:f>Sheet1!$A$2:$A$20</c:f>
               <c:strCache>
-                <c:ptCount val="20"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>Fixed Object</c:v>
                 </c:pt>
@@ -406,109 +397,103 @@
                   <c:v>Overturning</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>Parked Vehicle</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>Pedalcycles</c:v>
                 </c:pt>
-                <c:pt idx="9">
-                  <c:v>Parked Vehicle</c:v>
-                </c:pt>
                 <c:pt idx="10">
+                  <c:v>Animal</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>Other Non-Collision</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>Animal</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>Right Turn</c:v>
                 </c:pt>
                 <c:pt idx="13">
+                  <c:v>Unknown</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Other Object</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>Sideswipe - Meeting</c:v>
                 </c:pt>
-                <c:pt idx="14">
-                  <c:v>Unknown</c:v>
-                </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>Backing</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
+                  <c:v>Other Non-Vehicle</c:v>
+                </c:pt>
+                <c:pt idx="18">
                   <c:v>Train</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>Other Object</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>Falling From Or In Vehicle</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>Other Non-Vehicle</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$2:$C$21</c:f>
+              <c:f>Sheet1!$C$2:$C$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>24.12164714771439</c:v>
+                  <c:v>23.83124287343215</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>10.88024178315074</c:v>
+                  <c:v>11.59255036107944</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>18.43596524367208</c:v>
+                  <c:v>18.5480805777271</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7.857952398942198</c:v>
+                  <c:v>7.829722538958571</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10.1057801284473</c:v>
+                  <c:v>9.59711136450019</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>7.857952398942198</c:v>
+                  <c:v>7.791714177118966</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>6.800151114469211</c:v>
+                  <c:v>6.404408969973393</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.211182470721571</c:v>
+                  <c:v>3.287723299125807</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.097846618813751</c:v>
+                  <c:v>2.508551881413911</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.342274272761617</c:v>
+                  <c:v>3.211706575446598</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.96448809973555</c:v>
+                  <c:v>1.026225769669327</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.020022667170382</c:v>
+                  <c:v>2.090459901178259</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.246694370986022</c:v>
+                  <c:v>1.235271759787153</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.03777861730260672</c:v>
+                  <c:v>0.4561003420752566</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.4533434076312807</c:v>
+                  <c:v>0.1520334473584188</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.3588968643747639</c:v>
+                  <c:v>0.03800836183960471</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.01888930865130336</c:v>
+                  <c:v>0.3800836183960471</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.1888930865130336</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0</c:v>
+                  <c:v>0.01900418091980235</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -538,9 +523,9 @@
           </c:spPr>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$A$2:$A$21</c:f>
+              <c:f>Sheet1!$A$2:$A$20</c:f>
               <c:strCache>
-                <c:ptCount val="20"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>Fixed Object</c:v>
                 </c:pt>
@@ -566,109 +551,103 @@
                   <c:v>Overturning</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>Parked Vehicle</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>Pedalcycles</c:v>
                 </c:pt>
-                <c:pt idx="9">
-                  <c:v>Parked Vehicle</c:v>
-                </c:pt>
                 <c:pt idx="10">
+                  <c:v>Animal</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>Other Non-Collision</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>Animal</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>Right Turn</c:v>
                 </c:pt>
                 <c:pt idx="13">
+                  <c:v>Unknown</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Other Object</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>Sideswipe - Meeting</c:v>
                 </c:pt>
-                <c:pt idx="14">
-                  <c:v>Unknown</c:v>
-                </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>Backing</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
+                  <c:v>Other Non-Vehicle</c:v>
+                </c:pt>
+                <c:pt idx="18">
                   <c:v>Train</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>Other Object</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>Falling From Or In Vehicle</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>Other Non-Vehicle</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$D$2:$D$21</c:f>
+              <c:f>Sheet1!$D$2:$D$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>15.27325944052589</c:v>
+                  <c:v>15.50065019505852</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.415958927114822</c:v>
+                  <c:v>1.535480251918713</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>14.77856148937191</c:v>
+                  <c:v>15.31043626813534</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.013818914639413</c:v>
+                  <c:v>2.159667508095566</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>23.6140300369464</c:v>
+                  <c:v>22.11836099849562</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6.558706396046254</c:v>
+                  <c:v>6.691144598281445</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>14.85677270764359</c:v>
+                  <c:v>14.69950789158316</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.6482414471474497</c:v>
+                  <c:v>0.6782426884928224</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.6031380451993666</c:v>
+                  <c:v>6.344883857314057</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>6.279928986133103</c:v>
+                  <c:v>0.6231673423595706</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.400124754090495</c:v>
+                  <c:v>5.095489431143069</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>4.880284055467588</c:v>
+                  <c:v>1.48856421632372</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.964828942948995</c:v>
+                  <c:v>2.969989035926464</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.051341106472818</c:v>
+                  <c:v>0.6190876870904408</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.5709898757257329</c:v>
+                  <c:v>0.4630408730462275</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>3.632743150520608</c:v>
+                  <c:v>0.05609525995053418</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.01007629192457176</c:v>
+                  <c:v>3.633442974068691</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.4457559618060554</c:v>
+                  <c:v>0.00101991381728244</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.0004798234249796075</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0.000959646849959215</c:v>
+                  <c:v>0.01172900889874806</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1096,7 +1075,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.7109375" style="1" customWidth="1"/>
@@ -1124,13 +1103,13 @@
         <v>4</v>
       </c>
       <c r="B2" s="2">
-        <v>30.02915451895043</v>
+        <v>28.55740922473013</v>
       </c>
       <c r="C2" s="2">
-        <v>24.12164714771439</v>
+        <v>23.83124287343215</v>
       </c>
       <c r="D2" s="2">
-        <v>15.27325944052589</v>
+        <v>15.50065019505852</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1138,13 +1117,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="2">
-        <v>17.58989310009718</v>
+        <v>17.46810598626104</v>
       </c>
       <c r="C3" s="2">
-        <v>10.88024178315074</v>
+        <v>11.59255036107944</v>
       </c>
       <c r="D3" s="2">
-        <v>1.415958927114822</v>
+        <v>1.535480251918713</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1152,13 +1131,13 @@
         <v>6</v>
       </c>
       <c r="B4" s="2">
-        <v>12.53644314868805</v>
+        <v>14.22963689892051</v>
       </c>
       <c r="C4" s="2">
-        <v>18.43596524367208</v>
+        <v>18.5480805777271</v>
       </c>
       <c r="D4" s="2">
-        <v>14.77856148937191</v>
+        <v>15.31043626813534</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1166,13 +1145,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="2">
-        <v>11.07871720116618</v>
+        <v>11.48184494602552</v>
       </c>
       <c r="C5" s="2">
-        <v>7.857952398942198</v>
+        <v>7.829722538958571</v>
       </c>
       <c r="D5" s="2">
-        <v>2.013818914639413</v>
+        <v>2.159667508095566</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1180,13 +1159,13 @@
         <v>8</v>
       </c>
       <c r="B6" s="2">
-        <v>6.997084548104956</v>
+        <v>7.065750736015702</v>
       </c>
       <c r="C6" s="2">
-        <v>10.1057801284473</v>
+        <v>9.59711136450019</v>
       </c>
       <c r="D6" s="2">
-        <v>23.6140300369464</v>
+        <v>22.11836099849562</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1194,13 +1173,13 @@
         <v>9</v>
       </c>
       <c r="B7" s="2">
-        <v>6.608357628765791</v>
+        <v>6.182531894013739</v>
       </c>
       <c r="C7" s="2">
-        <v>7.857952398942198</v>
+        <v>7.791714177118966</v>
       </c>
       <c r="D7" s="2">
-        <v>6.558706396046254</v>
+        <v>6.691144598281445</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1208,13 +1187,13 @@
         <v>10</v>
       </c>
       <c r="B8" s="2">
-        <v>4.859086491739554</v>
+        <v>5.397448478900883</v>
       </c>
       <c r="C8" s="2">
-        <v>6.800151114469211</v>
+        <v>6.404408969973393</v>
       </c>
       <c r="D8" s="2">
-        <v>14.85677270764359</v>
+        <v>14.69950789158316</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1222,13 +1201,13 @@
         <v>11</v>
       </c>
       <c r="B9" s="2">
-        <v>3.109815354713314</v>
+        <v>3.042198233562316</v>
       </c>
       <c r="C9" s="2">
-        <v>3.211182470721571</v>
+        <v>3.287723299125807</v>
       </c>
       <c r="D9" s="2">
-        <v>0.6482414471474497</v>
+        <v>0.6782426884928224</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1236,13 +1215,13 @@
         <v>12</v>
       </c>
       <c r="B10" s="2">
-        <v>1.84645286686103</v>
+        <v>1.962708537782139</v>
       </c>
       <c r="C10" s="2">
-        <v>3.097846618813751</v>
+        <v>2.508551881413911</v>
       </c>
       <c r="D10" s="2">
-        <v>0.6031380451993666</v>
+        <v>6.344883857314057</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1250,13 +1229,13 @@
         <v>13</v>
       </c>
       <c r="B11" s="2">
-        <v>1.652089407191448</v>
+        <v>1.275760549558391</v>
       </c>
       <c r="C11" s="2">
-        <v>2.342274272761617</v>
+        <v>3.211706575446598</v>
       </c>
       <c r="D11" s="2">
-        <v>6.279928986133103</v>
+        <v>0.6231673423595706</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1264,13 +1243,13 @@
         <v>14</v>
       </c>
       <c r="B12" s="2">
-        <v>1.068999028182702</v>
+        <v>1.079489695780177</v>
       </c>
       <c r="C12" s="2">
-        <v>1.96448809973555</v>
+        <v>1.026225769669327</v>
       </c>
       <c r="D12" s="2">
-        <v>1.400124754090495</v>
+        <v>5.095489431143069</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1278,13 +1257,13 @@
         <v>15</v>
       </c>
       <c r="B13" s="2">
-        <v>0.9718172983479106</v>
+        <v>0.8832188420019628</v>
       </c>
       <c r="C13" s="2">
-        <v>1.020022667170382</v>
+        <v>2.090459901178259</v>
       </c>
       <c r="D13" s="2">
-        <v>4.880284055467588</v>
+        <v>1.48856421632372</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1292,13 +1271,13 @@
         <v>16</v>
       </c>
       <c r="B14" s="2">
-        <v>0.9718172983479106</v>
+        <v>0.7850834151128557</v>
       </c>
       <c r="C14" s="2">
-        <v>1.246694370986022</v>
+        <v>1.235271759787153</v>
       </c>
       <c r="D14" s="2">
-        <v>2.964828942948995</v>
+        <v>2.969989035926464</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1306,13 +1285,13 @@
         <v>17</v>
       </c>
       <c r="B15" s="2">
-        <v>0.1943634596695821</v>
+        <v>0.2944062806673209</v>
       </c>
       <c r="C15" s="2">
-        <v>0.03777861730260672</v>
+        <v>0.4561003420752566</v>
       </c>
       <c r="D15" s="2">
-        <v>0.051341106472818</v>
+        <v>0.6190876870904408</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1320,13 +1299,13 @@
         <v>18</v>
       </c>
       <c r="B16" s="2">
-        <v>0.1943634596695821</v>
+        <v>0.09813542688910697</v>
       </c>
       <c r="C16" s="2">
-        <v>0.4533434076312807</v>
+        <v>0.1520334473584188</v>
       </c>
       <c r="D16" s="2">
-        <v>0.5709898757257329</v>
+        <v>0.4630408730462275</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1334,13 +1313,13 @@
         <v>19</v>
       </c>
       <c r="B17" s="2">
-        <v>0.09718172983479105</v>
+        <v>0.09813542688910697</v>
       </c>
       <c r="C17" s="2">
-        <v>0.3588968643747639</v>
+        <v>0.03800836183960471</v>
       </c>
       <c r="D17" s="2">
-        <v>3.632743150520608</v>
+        <v>0.05609525995053418</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1348,13 +1327,13 @@
         <v>20</v>
       </c>
       <c r="B18" s="2">
-        <v>0.09718172983479105</v>
+        <v>0.09813542688910697</v>
       </c>
       <c r="C18" s="2">
-        <v>0.01888930865130336</v>
+        <v>0.3800836183960471</v>
       </c>
       <c r="D18" s="2">
-        <v>0.01007629192457176</v>
+        <v>3.633442974068691</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1362,13 +1341,13 @@
         <v>21</v>
       </c>
       <c r="B19" s="2">
-        <v>0.09718172983479105</v>
+        <v>0</v>
       </c>
       <c r="C19" s="2">
-        <v>0.1888930865130336</v>
+        <v>0</v>
       </c>
       <c r="D19" s="2">
-        <v>0.4457559618060554</v>
+        <v>0.00101991381728244</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1379,24 +1358,10 @@
         <v>0</v>
       </c>
       <c r="C20" s="2">
-        <v>0</v>
+        <v>0.01900418091980235</v>
       </c>
       <c r="D20" s="2">
-        <v>0.0004798234249796075</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B21" s="2">
-        <v>0</v>
-      </c>
-      <c r="C21" s="2">
-        <v>0</v>
-      </c>
-      <c r="D21" s="2">
-        <v>0.000959646849959215</v>
+        <v>0.01172900889874806</v>
       </c>
     </row>
   </sheetData>

--- a/output_data/charts/crashSeverityByType-Region10.xlsx
+++ b/output_data/charts/crashSeverityByType-Region10.xlsx
@@ -89,8 +89,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode=""/>
+    <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -147,7 +148,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -179,7 +180,7 @@
               <a:rPr lang="en-US" sz="1400" baseline="0">
                 <a:latin typeface="Arial"/>
               </a:rPr>
-              <a:t>Crash Severity by Type of Crash - 10-County Region</a:t>
+              <a:t>Crash Severity by Type of Crash, 10-County Region, 2020-2024</a:t>
             </a:r>
           </a:p>
         </c:rich>
